--- a/artfynd/A 59690-2019 artfynd.xlsx
+++ b/artfynd/A 59690-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118547599</v>
+        <v>118547598</v>
       </c>
       <c r="B2" t="n">
-        <v>97883</v>
+        <v>58105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433837</v>
+        <v>433816</v>
       </c>
       <c r="R2" t="n">
-        <v>6406930</v>
+        <v>6406905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118547598</v>
+        <v>118547599</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>97883</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433816</v>
+        <v>433837</v>
       </c>
       <c r="R3" t="n">
-        <v>6406905</v>
+        <v>6406930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 59690-2019 artfynd.xlsx
+++ b/artfynd/A 59690-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118547598</v>
+        <v>118547599</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>97883</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>219875</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433816</v>
+        <v>433837</v>
       </c>
       <c r="R2" t="n">
-        <v>6406905</v>
+        <v>6406930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118547599</v>
+        <v>118547598</v>
       </c>
       <c r="B3" t="n">
-        <v>97883</v>
+        <v>58105</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219875</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433837</v>
+        <v>433816</v>
       </c>
       <c r="R3" t="n">
-        <v>6406930</v>
+        <v>6406905</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 59690-2019 artfynd.xlsx
+++ b/artfynd/A 59690-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118547599</v>
+        <v>118547598</v>
       </c>
       <c r="B2" t="n">
-        <v>97883</v>
+        <v>58105</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433837</v>
+        <v>433816</v>
       </c>
       <c r="R2" t="n">
-        <v>6406930</v>
+        <v>6406905</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118547598</v>
+        <v>118547608</v>
       </c>
       <c r="B3" t="n">
-        <v>58105</v>
+        <v>74415</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433816</v>
+        <v>433896</v>
       </c>
       <c r="R3" t="n">
-        <v>6406905</v>
+        <v>6406976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118547608</v>
+        <v>118547599</v>
       </c>
       <c r="B4" t="n">
-        <v>74408</v>
+        <v>97890</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6428</v>
+        <v>219875</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433896</v>
+        <v>433837</v>
       </c>
       <c r="R4" t="n">
-        <v>6406976</v>
+        <v>6406930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 59690-2019 artfynd.xlsx
+++ b/artfynd/A 59690-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118547598</v>
+        <v>118547608</v>
       </c>
       <c r="B2" t="n">
-        <v>58105</v>
+        <v>74415</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>6428</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>433816</v>
+        <v>433896</v>
       </c>
       <c r="R2" t="n">
-        <v>6406905</v>
+        <v>6406976</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118547608</v>
+        <v>118547599</v>
       </c>
       <c r="B3" t="n">
-        <v>74415</v>
+        <v>97890</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6428</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>433896</v>
+        <v>433837</v>
       </c>
       <c r="R3" t="n">
-        <v>6406976</v>
+        <v>6406930</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-07-11</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118547599</v>
+        <v>118547598</v>
       </c>
       <c r="B4" t="n">
-        <v>97890</v>
+        <v>58105</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +895,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219875</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Viken, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433837</v>
+        <v>433816</v>
       </c>
       <c r="R4" t="n">
-        <v>6406930</v>
+        <v>6406905</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
